--- a/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +50,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,212 +420,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Значение</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ИНВЕНТАРНАЯ КАРТОЧКА ОРГТЕХНИКИ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Документ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ИНВЕНТАРНАЯ КАРТОЧКА ОРГТЕХНИКИ</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Организация: Этажи</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Дата составления</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>22.06.2026</t>
-        </is>
-      </c>
+      <c r="A3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>№ п/п</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Дата составления: 22.06.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Инвентарный номер</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>67+</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>№ п/п: 1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Марка / модель</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kyocera ECOSYS M3040dn</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Серийный номер</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LS67Y43279</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Инвентарный номер: 67+</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Место размещения</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Риелторы (Тюмень)</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Марка / модель: Kyocera ECOSYS M3040dn</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Офис</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Тюмень</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Серийный номер: LS67Y43279</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Подразделение</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Риелторы</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Место размещения: Риелторы (Тюмень)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Счетчик (предыдущий месяц)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>272339</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Офис: Тюмень</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Счетчик (отчетный месяц)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>272864</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Подразделение: Риелторы</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Кол-во отпечатков</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ответственный</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Счетчик (предыдущий месяц): 272339</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Исправно / Неисправно</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Счетчик (отчетный месяц): 272864</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Кол-во отпечатков: 525</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Материально ответственное лицо</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Инвентаризатор</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ответственный сотрудник: </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Состояние оборудования: Исправно / Неисправно</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Примечание:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Материально ответственное лицо: __________________ / __________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Инвентаризатор: __________________ / __________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Подписи. М.П.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -429,156 +429,685 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ИНВЕНТАРНАЯ КАРТОЧКА ОРГТЕХНИКИ</t>
+          <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Организация: Этажи</t>
+          <t xml:space="preserve">КАРТОЧКА АППАРАТА № 67+    Дата: 22.06.2026  </t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Инженеры: Антон / Александр</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Дата составления: 22.06.2026</t>
+          <t>═══════════════════════════════════════════════════════════════</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>№ п/п: 1</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>1. ИДЕНТИФИКАЦИЯ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Инвентарный номер: 67+</t>
+          <t>───────────────────────────────────────────────────────────────</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Марка / модель: Kyocera ECOSYS M3040dn</t>
+          <t xml:space="preserve">Модель:                  Kyocera ECOSYS M3040dn               </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Серийный номер: LS67Y43279</t>
+          <t xml:space="preserve">Серийный номер:          LS67Y43279                           </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Место размещения: Риелторы (Тюмень)</t>
+          <t xml:space="preserve">Инвентарный номер:       67+                                  </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Офис: Тюмень</t>
+          <t xml:space="preserve">Локация (офис/кабинет):  Риелторы (Тюмень)                    </t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Подразделение: Риелторы</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2. РЕКВИЗИТЫ ДЛЯ АНАЛИЗА</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Счетчик (предыдущий месяц): 272339</t>
+          <t>───────────────────────────────────────────────────────────────</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Счетчик (отчетный месяц): 272864</t>
+          <t>IP-адрес:                _____________________________________</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Кол-во отпечатков: 525</t>
+          <t>MAC-адрес:               _____________________________________</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr"/>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Модель картриджа:        _____________________________________</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ответственный сотрудник: </t>
+          <t>Текущий ресурс картриджа (%): ________________________________</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Версия прошивки:         _____________________________________</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Состояние оборудования: Исправно / Неисправно</t>
+          <t>Дата последнего ТО:      _____________________________________</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Примечание:</t>
+          <t>Дата последней замены ЗИП: ___________________________________</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ответственный у Заказчика: ___________________________________</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Материально ответственное лицо: __________________ / __________________</t>
+          <t>Контакт (тел/email):     _____________________________________</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Инвентаризатор: __________________ / __________________</t>
-        </is>
-      </c>
+      <c r="A24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Подписи. М.П.</t>
+          <t>3. СЧЕТЧИКИ</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Общий пробег (Total):    272864       стр.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Ч/Б:                     ____________ стр.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Цветной:                 ____________ стр.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Сканер:                  ____________ стр.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Пробег с последнего ТО:  525          стр.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>4. ФИЗИЧЕСКОЕ СОСТОЯНИЕ (отметить ✓ или ✗)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Корпус без трещин, крышки закрываются</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Лоток подачи бумаги: ролики чистые, не лысые, пружины целые</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Лоток выхода: флажки/направляющие целые</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Дуплекс-модуль: нет замятий, засохшего тонера</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Внутренность: нет рассыпанного тонера, бумаги, скрепок</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Кабель питания / USB — целые, с запасом</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Шум при работе: нет треска, скрежета, вибрации</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>5. КАЧЕСТВО ПЕЧАТИ (распечатать тестовую страницу из меню)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Равномерная плотность по всей странице</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Нет вертикальных полос / точек / фона</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Нет "волн" и повторяющихся дефектов (шаг дефекта: _____ мм)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Регистрация листа ровная (текст не уходит вбок)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Тонер закреплен (не смазывается пальцем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>6. КАЧЕСТВО СКАНИРОВАНИЯ (протестировать на A4 и A3 если есть ADF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>[ ] ADF захватывает лист без перекоса</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>[ ] На скане нет полос (проверить стекло и зеркало)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Скан в сетевую папку / на email работает</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>[ ] Двустороннее сканирование работает (если есть)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>7. СУБЪЕКТИВНАЯ ОЦЕНКА СОСТОЯНИЯ (1-5 баллов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Шкала оценки:</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1 — Критическое (не работает / требует срочного ремонта)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2 — Плохое (работает с перебоями / явные дефекты качества)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3 — Удовлетворительное (работает, но требует внимания/ТО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4 — Хорошее (работает стабильно, мелкие замечания)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5 — Отличное (идеальное состояние, как новый)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Физическое состояние:    [ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>Качество печати:         [ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Качество сканирования:   [ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>Общая оценка:            [ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий к оценке:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>________________________________________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>________________________________________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>8. ЗАМЕЧЕНИЯ И "БОЛЯЧКИ" (свободное описание)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>________________________________________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>________________________________________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>________________________________________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>9. ПЛАН ДЕЙСТВИЙ (отметить все применимые пункты)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>───────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>[ 1 ] Не требует действий — аппарат в рабочем состоянии</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>[ 2 ] Требуется профилактическая чистка (внутренняя/внешняя)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>[ 3 ] Требуется плановое ТО (замена роликов, чистка лазера)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>[ 4 ] Требуется замена ЗИП (указать что: _____________________)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>[ 5 ] Требуется замена картриджа / тонера</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>[ 6 ] Требуется калибровка цвета (для цветных аппаратов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>[ 7 ] Требуется замена термоузла / печки</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>[ 8 ] Требуется перепрошивка / обновление встроенного ПО</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>[ 9 ] Требуется перемещение в другую локацию / кабинет</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>[10 ] Требуется обучение пользователя / инструктаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>[11 ] Требуется эскалация в вендора / авторизованный СЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>[12 ] Требуется списание / утилизация (обоснование: ____________)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>[13 ] Требуется согласование с Заказчиком (ИТ / АХО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>[14 ] Требуется срочная закупка расходных материалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>[15 ] Аппарат временно выведен из эксплуатации (до: ____________)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Приоритет выполнения:  🔴 Критичный  /  🟡 Средний  /  🟢 Плановый</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Срок выполнения:       _____________________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>ПОДПИСИ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>Антон: _______________     Александр: _______________</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>═══════════════════════════════════════════════════════════════</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
@@ -413,13 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,6 +441,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Отметка</t>
         </is>
       </c>
@@ -457,6 +463,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -475,6 +482,7 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,6 +501,7 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -511,6 +520,7 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -525,6 +535,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -539,6 +550,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,6 +565,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -571,6 +584,7 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -589,6 +603,7 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -607,6 +622,7 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,6 +641,7 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -639,6 +656,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -653,6 +671,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -667,6 +686,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -681,6 +701,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -695,6 +716,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -709,6 +731,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -723,6 +746,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -737,6 +761,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -751,6 +776,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -765,6 +791,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -779,6 +806,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -793,6 +821,7 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -807,6 +836,7 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -821,10 +851,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>272864       стр.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>272864</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>стр.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -838,7 +873,12 @@
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>стр.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -852,7 +892,12 @@
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>стр.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -866,7 +911,12 @@
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>стр.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -881,10 +931,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>525          стр.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>стр.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -899,6 +954,7 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -913,6 +969,7 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -927,6 +984,11 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -941,6 +1003,11 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -955,6 +1022,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -969,6 +1041,11 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -983,6 +1060,11 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -997,6 +1079,11 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1011,6 +1098,11 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1025,6 +1117,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1039,6 +1132,7 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1053,6 +1147,11 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1067,6 +1166,11 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1079,8 +1183,17 @@
           <t>Нет "волн" и повторяющихся дефектов (шаг дефекта: _____ мм)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>мм)</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1095,6 +1208,11 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1109,6 +1227,11 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1123,6 +1246,7 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1137,6 +1261,7 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1151,6 +1276,11 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1165,6 +1295,11 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1179,6 +1314,11 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1193,6 +1333,11 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1207,6 +1352,7 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1221,6 +1367,7 @@
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1235,6 +1382,7 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1249,6 +1397,7 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1263,6 +1412,7 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1277,6 +1427,7 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1291,6 +1442,7 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1305,11 +1457,12 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Оценка</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1317,17 +1470,18 @@
           <t>Физическое состояние</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
         <is>
           <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Оценка</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1335,17 +1489,18 @@
           <t>Качество печати</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
         <is>
           <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Оценка</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1353,17 +1508,18 @@
           <t>Качество сканирования</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
         <is>
           <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Оценка</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1371,12 +1527,13 @@
           <t>Общая оценка</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
         <is>
           <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1391,6 +1548,7 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1405,6 +1563,7 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1419,6 +1578,7 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1433,6 +1593,7 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1447,6 +1608,7 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1461,6 +1623,7 @@
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1475,6 +1638,7 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1489,6 +1653,7 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1507,6 +1672,7 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1521,6 +1687,7 @@
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1535,6 +1702,7 @@
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1549,6 +1717,7 @@
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1563,6 +1732,7 @@
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1577,6 +1747,7 @@
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1591,6 +1762,7 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1605,6 +1777,7 @@
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1623,6 +1796,7 @@
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1637,6 +1811,7 @@
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1651,6 +1826,7 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1669,6 +1845,7 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1687,6 +1864,7 @@
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1701,6 +1879,7 @@
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1715,6 +1894,7 @@
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1727,8 +1907,13 @@
           <t>Антон</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Александр:</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1743,6 +1928,7 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
+++ b/equipment-templates/output/device-cards/TEST_Card_67plus_LS67Y43279.xlsx
@@ -1183,11 +1183,7 @@
           <t>Нет "волн" и повторяющихся дефектов (шаг дефекта: _____ мм)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>мм)</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
